--- a/reports/pdf_rolling5_20260831.xlsx
+++ b/reports/pdf_rolling5_20260831.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,586억   ·   현금 66억(1.4%)      오늘 2026-08-31  vs  5일전 2026-08-24      매수 14종목  /  매도 16종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,586억   ·   현금 33억(0.7%)      오늘 2026-08-31  vs  5일전 2026-08-24      매수 14종목  /  매도 16종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -927,23 +927,23 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>티씨케이  (신규)</t>
         </is>
       </c>
       <c r="B12" s="11" t="n">
         <v>18</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>2220168600</v>
+        <v>4408911000</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>3.63%→4.35%</t>
+          <t>0.00%→0.97%</t>
         </is>
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
-          <t>143→161</t>
+          <t>0→18</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
@@ -971,23 +971,23 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>티씨케이  (신규)</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="B13" s="11" t="n">
         <v>18</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>4408911000</v>
+        <v>2220168600</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.97%</t>
+          <t>3.63%→4.35%</t>
         </is>
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
-          <t>0→18</t>
+          <t>143→161</t>
         </is>
       </c>
       <c r="G13" s="14" t="inlineStr">
@@ -1191,23 +1191,23 @@
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="B18" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>734818500</v>
+        <v>985920000</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>2.83%→3.06%</t>
+          <t>7.11%→6.98%</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>54→57</t>
+          <t>94→97</t>
         </is>
       </c>
       <c r="G18" s="14" t="inlineStr">
@@ -1235,44 +1235,44 @@
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="B19" s="11" t="n">
         <v>3</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>985920000</v>
+        <v>734818500</v>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>7.11%→6.98%</t>
+          <t>2.83%→3.06%</t>
         </is>
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>94→97</t>
+          <t>54→57</t>
         </is>
       </c>
       <c r="G19" s="14" t="inlineStr">
         <is>
-          <t>에스엔시스</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="H19" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-102083800</v>
+        <v>-414908000</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
-          <t>0.63%→0.65%</t>
+          <t>1.54%→1.39%</t>
         </is>
       </c>
       <c r="K19" s="13" t="inlineStr">
         <is>
-          <t>120→116</t>
+          <t>65→61</t>
         </is>
       </c>
     </row>
@@ -1284,23 +1284,23 @@
       <c r="E20" s="17" t="n"/>
       <c r="G20" s="14" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>에스엔시스</t>
         </is>
       </c>
       <c r="H20" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-414908000</v>
+        <v>-102083800</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
-          <t>1.54%→1.39%</t>
+          <t>0.63%→0.65%</t>
         </is>
       </c>
       <c r="K20" s="13" t="inlineStr">
         <is>
-          <t>65→61</t>
+          <t>120→116</t>
         </is>
       </c>
     </row>
@@ -1335,7 +1335,7 @@
     <row r="23" ht="19" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,961억   ·   현금 25억(0.6%)      오늘 2026-08-31  vs  5일전 2026-08-24      매수 5종목  /  매도 3종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,961억   ·   현금 12억(0.3%)      오늘 2026-08-31  vs  5일전 2026-08-24      매수 5종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B23" s="4" t="n"/>
@@ -1612,7 +1612,7 @@
     <row r="32" ht="19" customHeight="1">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,614억   ·   현금 72억(2.7%)      오늘 2026-08-31  vs  5일전 2026-08-24      매수 7종목  /  매도 9종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,614억   ·   현금 36억(1.4%)      오늘 2026-08-31  vs  5일전 2026-08-24      매수 7종목  /  매도 9종목</t>
         </is>
       </c>
       <c r="B32" s="4" t="n"/>
@@ -2065,7 +2065,7 @@
     <row r="45" ht="19" customHeight="1">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,251억   ·   현금 54억(2.4%)      오늘 2026-08-31  vs  5일전 2026-08-24      매수 7종목  /  매도 3종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,251억   ·   현금 27억(1.2%)      오늘 2026-08-31  vs  5일전 2026-08-24      매수 7종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B45" s="4" t="n"/>
@@ -2398,7 +2398,7 @@
     <row r="56" ht="19" customHeight="1">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 278억   ·   현금 4억(1.5%)      오늘 2026-08-31  vs  5일전 2026-08-24      매수 14종목  /  매도 10종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 278억   ·   현금 2억(0.7%)      오늘 2026-08-31  vs  5일전 2026-08-24      매수 14종목  /  매도 10종목</t>
         </is>
       </c>
       <c r="B56" s="4" t="n"/>
@@ -2772,23 +2772,23 @@
       </c>
       <c r="G65" s="14" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>원익IPS</t>
         </is>
       </c>
       <c r="H65" s="15" t="n">
         <v>-10</v>
       </c>
       <c r="I65" s="15" t="n">
-        <v>-86472000</v>
+        <v>-79992000</v>
       </c>
       <c r="J65" s="16" t="inlineStr">
         <is>
-          <t>3.33%→3.04%</t>
+          <t>2.74%→2.46%</t>
         </is>
       </c>
       <c r="K65" s="13" t="inlineStr">
         <is>
-          <t>107→97</t>
+          <t>95→85</t>
         </is>
       </c>
     </row>
@@ -2816,23 +2816,23 @@
       </c>
       <c r="G66" s="14" t="inlineStr">
         <is>
-          <t>원익IPS</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="H66" s="15" t="n">
         <v>-10</v>
       </c>
       <c r="I66" s="15" t="n">
-        <v>-79992000</v>
+        <v>-86472000</v>
       </c>
       <c r="J66" s="16" t="inlineStr">
         <is>
-          <t>2.74%→2.46%</t>
+          <t>3.33%→3.04%</t>
         </is>
       </c>
       <c r="K66" s="13" t="inlineStr">
         <is>
-          <t>95→85</t>
+          <t>107→97</t>
         </is>
       </c>
     </row>
@@ -2955,23 +2955,23 @@
     <row r="70">
       <c r="A70" s="10" t="inlineStr">
         <is>
-          <t>씨엠티엑스</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="B70" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C70" s="11" t="n">
-        <v>36540000</v>
+        <v>31903200</v>
       </c>
       <c r="D70" s="12" t="inlineStr">
         <is>
-          <t>0.79%→0.93%</t>
+          <t>0.97%→1.09%</t>
         </is>
       </c>
       <c r="E70" s="13" t="inlineStr">
         <is>
-          <t>42→49</t>
+          <t>59→66</t>
         </is>
       </c>
       <c r="G70" s="17" t="n"/>
@@ -3011,23 +3011,23 @@
     <row r="72">
       <c r="A72" s="10" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>씨엠티엑스</t>
         </is>
       </c>
       <c r="B72" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C72" s="11" t="n">
-        <v>31903200</v>
+        <v>36540000</v>
       </c>
       <c r="D72" s="12" t="inlineStr">
         <is>
-          <t>0.97%→1.09%</t>
+          <t>0.79%→0.93%</t>
         </is>
       </c>
       <c r="E72" s="13" t="inlineStr">
         <is>
-          <t>59→66</t>
+          <t>42→49</t>
         </is>
       </c>
       <c r="G72" s="17" t="n"/>
@@ -3039,7 +3039,7 @@
     <row r="74" ht="19" customHeight="1">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 566억   ·   현금 5억(0.9%)      오늘 2026-08-31  vs  5일전 2026-08-24      매수 0종목  /  매도 0종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 566억   ·   현금 3억(0.5%)      오늘 2026-08-31  vs  5일전 2026-08-24      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B74" s="4" t="n"/>

--- a/reports/pdf_rolling5_20260831.xlsx
+++ b/reports/pdf_rolling5_20260831.xlsx
@@ -927,23 +927,23 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>티씨케이  (신규)</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="B12" s="11" t="n">
         <v>18</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>4408911000</v>
+        <v>2220168600</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.97%</t>
+          <t>3.63%→4.35%</t>
         </is>
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
-          <t>0→18</t>
+          <t>143→161</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
@@ -971,23 +971,23 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>티씨케이  (신규)</t>
         </is>
       </c>
       <c r="B13" s="11" t="n">
         <v>18</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>2220168600</v>
+        <v>4408911000</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>3.63%→4.35%</t>
+          <t>0.00%→0.97%</t>
         </is>
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
-          <t>143→161</t>
+          <t>0→18</t>
         </is>
       </c>
       <c r="G13" s="14" t="inlineStr">
@@ -2663,23 +2663,23 @@
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>스피어</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="B63" s="11" t="n">
         <v>26</v>
       </c>
       <c r="C63" s="11" t="n">
-        <v>41652000</v>
+        <v>99777600</v>
       </c>
       <c r="D63" s="12" t="inlineStr">
         <is>
-          <t>2.12%→2.28%</t>
+          <t>0.73%→1.10%</t>
         </is>
       </c>
       <c r="E63" s="13" t="inlineStr">
         <is>
-          <t>367→393</t>
+          <t>53→79</t>
         </is>
       </c>
       <c r="G63" s="14" t="inlineStr">
@@ -2707,23 +2707,23 @@
     <row r="64">
       <c r="A64" s="10" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>스피어</t>
         </is>
       </c>
       <c r="B64" s="11" t="n">
         <v>26</v>
       </c>
       <c r="C64" s="11" t="n">
-        <v>99777600</v>
+        <v>41652000</v>
       </c>
       <c r="D64" s="12" t="inlineStr">
         <is>
-          <t>0.73%→1.10%</t>
+          <t>2.12%→2.28%</t>
         </is>
       </c>
       <c r="E64" s="13" t="inlineStr">
         <is>
-          <t>53→79</t>
+          <t>367→393</t>
         </is>
       </c>
       <c r="G64" s="14" t="inlineStr">
@@ -2955,23 +2955,23 @@
     <row r="70">
       <c r="A70" s="10" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>씨엠티엑스</t>
         </is>
       </c>
       <c r="B70" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C70" s="11" t="n">
-        <v>31903200</v>
+        <v>36540000</v>
       </c>
       <c r="D70" s="12" t="inlineStr">
         <is>
-          <t>0.97%→1.09%</t>
+          <t>0.79%→0.93%</t>
         </is>
       </c>
       <c r="E70" s="13" t="inlineStr">
         <is>
-          <t>59→66</t>
+          <t>42→49</t>
         </is>
       </c>
       <c r="G70" s="17" t="n"/>
@@ -2983,23 +2983,23 @@
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="B71" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C71" s="11" t="n">
-        <v>55339200</v>
+        <v>31903200</v>
       </c>
       <c r="D71" s="12" t="inlineStr">
         <is>
-          <t>1.00%→1.20%</t>
+          <t>0.97%→1.09%</t>
         </is>
       </c>
       <c r="E71" s="13" t="inlineStr">
         <is>
-          <t>35→42</t>
+          <t>59→66</t>
         </is>
       </c>
       <c r="G71" s="17" t="n"/>
@@ -3011,23 +3011,23 @@
     <row r="72">
       <c r="A72" s="10" t="inlineStr">
         <is>
-          <t>씨엠티엑스</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="B72" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C72" s="11" t="n">
-        <v>36540000</v>
+        <v>55339200</v>
       </c>
       <c r="D72" s="12" t="inlineStr">
         <is>
-          <t>0.79%→0.93%</t>
+          <t>1.00%→1.20%</t>
         </is>
       </c>
       <c r="E72" s="13" t="inlineStr">
         <is>
-          <t>42→49</t>
+          <t>35→42</t>
         </is>
       </c>
       <c r="G72" s="17" t="n"/>

--- a/reports/pdf_rolling5_20260831.xlsx
+++ b/reports/pdf_rolling5_20260831.xlsx
@@ -927,23 +927,23 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>피에스케이홀딩스</t>
+          <t>티씨케이  (신규)</t>
         </is>
       </c>
       <c r="B12" s="11" t="n">
         <v>18</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>2220168600</v>
+        <v>4408911000</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>3.63%→4.35%</t>
+          <t>0.00%→0.97%</t>
         </is>
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
-          <t>143→161</t>
+          <t>0→18</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
@@ -971,23 +971,23 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>티씨케이  (신규)</t>
+          <t>피에스케이홀딩스</t>
         </is>
       </c>
       <c r="B13" s="11" t="n">
         <v>18</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>4408911000</v>
+        <v>2220168600</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.97%</t>
+          <t>3.63%→4.35%</t>
         </is>
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
-          <t>0→18</t>
+          <t>143→161</t>
         </is>
       </c>
       <c r="G13" s="14" t="inlineStr">
@@ -1256,23 +1256,23 @@
       </c>
       <c r="G19" s="14" t="inlineStr">
         <is>
-          <t>리가켐바이오</t>
+          <t>에스엔시스</t>
         </is>
       </c>
       <c r="H19" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I19" s="15" t="n">
-        <v>-414908000</v>
+        <v>-102083800</v>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
-          <t>1.54%→1.39%</t>
+          <t>0.63%→0.65%</t>
         </is>
       </c>
       <c r="K19" s="13" t="inlineStr">
         <is>
-          <t>65→61</t>
+          <t>120→116</t>
         </is>
       </c>
     </row>
@@ -1284,23 +1284,23 @@
       <c r="E20" s="17" t="n"/>
       <c r="G20" s="14" t="inlineStr">
         <is>
-          <t>에스엔시스</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="H20" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I20" s="15" t="n">
-        <v>-102083800</v>
+        <v>-414908000</v>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
-          <t>0.63%→0.65%</t>
+          <t>1.54%→1.39%</t>
         </is>
       </c>
       <c r="K20" s="13" t="inlineStr">
         <is>
-          <t>120→116</t>
+          <t>65→61</t>
         </is>
       </c>
     </row>
@@ -2955,23 +2955,23 @@
     <row r="70">
       <c r="A70" s="10" t="inlineStr">
         <is>
-          <t>씨엠티엑스</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="B70" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C70" s="11" t="n">
-        <v>36540000</v>
+        <v>55339200</v>
       </c>
       <c r="D70" s="12" t="inlineStr">
         <is>
-          <t>0.79%→0.93%</t>
+          <t>1.00%→1.20%</t>
         </is>
       </c>
       <c r="E70" s="13" t="inlineStr">
         <is>
-          <t>42→49</t>
+          <t>35→42</t>
         </is>
       </c>
       <c r="G70" s="17" t="n"/>
@@ -3011,23 +3011,23 @@
     <row r="72">
       <c r="A72" s="10" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>씨엠티엑스</t>
         </is>
       </c>
       <c r="B72" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C72" s="11" t="n">
-        <v>55339200</v>
+        <v>36540000</v>
       </c>
       <c r="D72" s="12" t="inlineStr">
         <is>
-          <t>1.00%→1.20%</t>
+          <t>0.79%→0.93%</t>
         </is>
       </c>
       <c r="E72" s="13" t="inlineStr">
         <is>
-          <t>35→42</t>
+          <t>42→49</t>
         </is>
       </c>
       <c r="G72" s="17" t="n"/>
